--- a/output/hmb/ALP-HMB-MIN-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-MIN-NG-100.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,10 +36,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -67,11 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1870,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2421,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3900,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -4018,14 +4013,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>net export 662.4 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
+          <t>net export 662.4 MW vs DP-OWNR-0051 connection capacity 640 MW (this case); capability above the capacity, export limited: 640 MW net at the 380 kV revenue meters (TQ-027, TP-E1)</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-MIN-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-MIN-NG-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-MIN-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-MIN-NG-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.40654341145627</v>
+        <v>9.966543411456266</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>662.3564565885437</v>
+        <v>662.7964565885437</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5739.774159842977</v>
+        <v>5735.963788491069</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.72023776103563</v>
+        <v>62.7619024935831</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.861195495075886</v>
+        <v>1.79600239013573</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gas flow 109,310 Sm3/h = 95.1 % of DP-OWNR-0033 (115,000 Sm3/h)</t>
+          <t>gas flow 109,310 Sm3/h = 91.1 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>net export 662.4 MW vs DP-OWNR-0051 connection capacity 640 MW (this case); capability above the capacity, export limited: 640 MW net at the 380 kV revenue meters (TQ-027, TP-E1)</t>
+          <t>net export 662.8 MW vs DP-OWNR-0051 connection capacity 640 MW (this case); capability above the capacity, export limited: 640 MW net at the 380 kV revenue meters (TQ-027, TP-E1)</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-MIN-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-MIN-NG-100.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -1831,6 +1831,56 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>source:SRC-IECE-0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>31</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fuel gas to the station preheater burners (water-bath heaters)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>fuel_gas</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FGS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PHB</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-41.94</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>preliminary</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>decision:DEC-EPCE-0014</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1870,7 +1920,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -2131,19 +2181,19 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>22.242</v>
+        <v>22.29</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2257,29 +2307,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>PHB</t>
         </is>
       </c>
       <c r="B14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>335.333</v>
+        <v>0.048</v>
       </c>
       <c r="D14" t="n">
-        <v>335.333</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1151.161</v>
+        <v>-0.002</v>
       </c>
       <c r="F14" t="n">
-        <v>1150.888</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.274</v>
+        <v>-0.002</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2289,29 +2339,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PIPE</t>
         </is>
       </c>
       <c r="B15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>335.333</v>
       </c>
       <c r="D15" t="n">
-        <v>10196.804</v>
+        <v>335.333</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1151.161</v>
       </c>
       <c r="F15" t="n">
-        <v>286.315</v>
+        <v>1150.888</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-286.315</v>
+        <v>0.274</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2321,70 +2371,102 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>233.688</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>233.689</v>
+        <v>10196.804</v>
       </c>
       <c r="E16" t="n">
-        <v>833.8869999999999</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>625.546</v>
+        <v>286.315</v>
       </c>
       <c r="G16" t="n">
-        <v>208.344</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.003</v>
+        <v>-286.315</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ST: shaft power (output / mechanical / generator efficiency)</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>233.688</v>
+      </c>
+      <c r="D17" t="n">
+        <v>233.689</v>
+      </c>
+      <c r="E17" t="n">
+        <v>833.8869999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>625.546</v>
+      </c>
+      <c r="G17" t="n">
+        <v>208.344</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ST: shaft power (output / mechanical / generator efficiency)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>STK</t>
         </is>
       </c>
-      <c r="B17" t="b">
+      <c r="B18" t="b">
         <v>1</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
         <v>823.529</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
         <v>44.425</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>44.425</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2421,7 +2503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3691,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1056.049020592244</v>
+        <v>1058.309066153803</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3639,7 +3721,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5735.963788491069</v>
+        <v>5748.239297722801</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3654,7 +3736,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.7619024935831</v>
+        <v>62.62787287624163</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3714,7 +3796,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22.242</v>
+        <v>22.2896</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3729,7 +3811,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>109310.2011956773</v>
+        <v>109544.1354451564</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3900,7 +3982,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4090,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gas flow 109,310 Sm3/h = 91.1 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
+          <t>gas flow 109,544 Sm3/h = 91.3 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-MIN-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-MIN-NG-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-MIN-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-MIN-NG-100.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -63,10 +67,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,7 +465,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1925,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2508,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3578,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3982,7 +3987,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -4083,24 +4088,36 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gas flow 109,544 Sm3/h = 91.3 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
+          <t>CW temperature rise 7.20 K vs DP-CASE-0015 &lt;= 7.0 K (Condenser cooling water temperature rise)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>gas flow 109,544 Sm3/h = 91.3 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>net export 662.8 MW vs DP-OWNR-0051 connection capacity 640 MW (this case); capability above the capacity, export limited: 640 MW net at the 380 kV revenue meters (TQ-027, TP-E1)</t>
         </is>
